--- a/examples/HFP_jon+jane.xlsx
+++ b/examples/HFP_jon+jane.xlsx
@@ -1937,8 +1937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1974,6 +1978,11 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>rate</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>property</t>
         </is>
       </c>
     </row>

--- a/examples/HFP_jon+jane.xlsx
+++ b/examples/HFP_jon+jane.xlsx
@@ -581,7 +581,7 @@
         <v>2026</v>
       </c>
       <c r="B7" t="n">
-        <v>120000</v>
+        <v>122000</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -597,6 +597,9 @@
       </c>
       <c r="L7" t="n">
         <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-2000</v>
       </c>
       <c r="N7" t="n">
         <v>4000</v>
@@ -607,7 +610,7 @@
         <v>2027</v>
       </c>
       <c r="B8" t="n">
-        <v>120000</v>
+        <v>122000</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -623,6 +626,9 @@
       </c>
       <c r="L8" t="n">
         <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-2000</v>
       </c>
       <c r="N8" t="n">
         <v>4000</v>
@@ -633,7 +639,7 @@
         <v>2028</v>
       </c>
       <c r="B9" t="n">
-        <v>120000</v>
+        <v>122000</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -649,6 +655,9 @@
       </c>
       <c r="L9" t="n">
         <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-2000</v>
       </c>
       <c r="N9" t="n">
         <v>4000</v>
@@ -659,7 +668,7 @@
         <v>2029</v>
       </c>
       <c r="B10" t="n">
-        <v>120000</v>
+        <v>122000</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -675,6 +684,9 @@
       </c>
       <c r="L10" t="n">
         <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-2000</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -685,7 +697,7 @@
         <v>2030</v>
       </c>
       <c r="B11" t="n">
-        <v>120000</v>
+        <v>122000</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -701,6 +713,9 @@
       </c>
       <c r="L11" t="n">
         <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-2000</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
